--- a/SP 2026 - tekme.xlsx
+++ b/SP 2026 - tekme.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="8985" yWindow="5115" windowWidth="28800" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="150" yWindow="150" windowWidth="23010" windowHeight="13650" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tekme" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skupine" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tekme" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Skupine" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" calcMode="manual" fullCalcOnLoad="1"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
     </row>

--- a/SP 2026 - tekme.xlsx
+++ b/SP 2026 - tekme.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="150" yWindow="150" windowWidth="23010" windowHeight="13650" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tekme" sheetId="1" state="visible" r:id="rId1"/>
@@ -581,11 +581,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M79"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="15.7109375" customWidth="1" style="17" min="1" max="1"/>
-    <col width="2.140625" customWidth="1" style="17" min="2" max="2"/>
-    <col width="15.7109375" customWidth="1" style="17" min="3" max="3"/>
+    <col width="15.6640625" customWidth="1" style="17" min="1" max="1"/>
+    <col width="2.109375" customWidth="1" style="17" min="2" max="2"/>
+    <col width="15.6640625" customWidth="1" style="17" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1" s="17">
@@ -673,7 +673,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3004,7 +3004,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
     </row>

--- a/SP 2026 - tekme.xlsx
+++ b/SP 2026 - tekme.xlsx
@@ -3,11 +3,12 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-23148" yWindow="-852" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tekme" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Skupine" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Izlocilni" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" calcMode="manual" fullCalcOnLoad="1"/>
@@ -17,10 +18,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <charset val="238"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -152,54 +160,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="16" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -581,14 +592,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M79"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15.6640625" customWidth="1" style="17" min="1" max="1"/>
-    <col width="2.109375" customWidth="1" style="17" min="2" max="2"/>
-    <col width="15.6640625" customWidth="1" style="17" min="3" max="3"/>
+    <col width="15.7109375" customWidth="1" style="18" min="1" max="1"/>
+    <col width="2.140625" customWidth="1" style="18" min="2" max="2"/>
+    <col width="15.7109375" customWidth="1" style="18" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1" s="17">
+    <row r="1" ht="19.5" customHeight="1" s="18">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>MEHIKA</t>
@@ -621,7 +632,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1" s="17">
+    <row r="2" ht="19.5" customHeight="1" s="18">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>J. KOREJA</t>
@@ -655,7 +666,7 @@
       </c>
       <c r="M2" s="1" t="n"/>
     </row>
-    <row r="3" ht="19.5" customHeight="1" s="17">
+    <row r="3" ht="19.5" customHeight="1" s="18">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ČEŠKA</t>
@@ -688,7 +699,7 @@
         <v>46191</v>
       </c>
     </row>
-    <row r="4" ht="19.5" customHeight="1" s="17">
+    <row r="4" ht="19.5" customHeight="1" s="18">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>MEHIKA</t>
@@ -721,7 +732,7 @@
         <v>46192</v>
       </c>
     </row>
-    <row r="5" ht="19.5" customHeight="1" s="17">
+    <row r="5" ht="19.5" customHeight="1" s="18">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ČEŠKA</t>
@@ -754,7 +765,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="6" ht="19.5" customHeight="1" s="17">
+    <row r="6" ht="19.5" customHeight="1" s="18">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>J. AFRIKA</t>
@@ -787,7 +798,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="7" ht="19.5" customHeight="1" s="17">
+    <row r="7" ht="19.5" customHeight="1" s="18">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>KANADA</t>
@@ -820,7 +831,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="8" ht="19.5" customHeight="1" s="17">
+    <row r="8" ht="19.5" customHeight="1" s="18">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>KATAR</t>
@@ -853,7 +864,7 @@
         <v>46186</v>
       </c>
     </row>
-    <row r="9" ht="19.5" customHeight="1" s="17">
+    <row r="9" ht="19.5" customHeight="1" s="18">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>ŠVICA</t>
@@ -886,7 +897,7 @@
         <v>46191</v>
       </c>
     </row>
-    <row r="10" ht="19.5" customHeight="1" s="17">
+    <row r="10" ht="19.5" customHeight="1" s="18">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>KANADA</t>
@@ -919,7 +930,7 @@
         <v>46192</v>
       </c>
     </row>
-    <row r="11" ht="19.5" customHeight="1" s="17">
+    <row r="11" ht="19.5" customHeight="1" s="18">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>ŠVICA</t>
@@ -952,7 +963,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1" s="17">
+    <row r="12" ht="19.5" customHeight="1" s="18">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>BiH</t>
@@ -985,7 +996,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="13" ht="19.5" customHeight="1" s="17">
+    <row r="13" ht="19.5" customHeight="1" s="18">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>BRAZILIJA</t>
@@ -1018,7 +1029,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1" s="17">
+    <row r="14" ht="19.5" customHeight="1" s="18">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>HAITI</t>
@@ -1051,7 +1062,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="15" ht="19.5" customHeight="1" s="17">
+    <row r="15" ht="19.5" customHeight="1" s="18">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>ŠKOTSKA</t>
@@ -1084,7 +1095,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="16" ht="19.5" customHeight="1" s="17">
+    <row r="16" ht="19.5" customHeight="1" s="18">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>BRAZILIJA</t>
@@ -1117,7 +1128,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="17" ht="19.5" customHeight="1" s="17">
+    <row r="17" ht="19.5" customHeight="1" s="18">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>ŠKOTSKA</t>
@@ -1150,7 +1161,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="18" ht="19.5" customHeight="1" s="17">
+    <row r="18" ht="19.5" customHeight="1" s="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>MAROKO</t>
@@ -1183,7 +1194,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="19" ht="19.5" customHeight="1" s="17">
+    <row r="19" ht="19.5" customHeight="1" s="18">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>ZDA</t>
@@ -1216,7 +1227,7 @@
         <v>46186</v>
       </c>
     </row>
-    <row r="20" ht="19.5" customHeight="1" s="17">
+    <row r="20" ht="19.5" customHeight="1" s="18">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>AVSTRALIJA</t>
@@ -1249,7 +1260,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="21" ht="19.5" customHeight="1" s="17">
+    <row r="21" ht="19.5" customHeight="1" s="18">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>ZDA</t>
@@ -1282,7 +1293,7 @@
         <v>46192</v>
       </c>
     </row>
-    <row r="22" ht="19.5" customHeight="1" s="17">
+    <row r="22" ht="19.5" customHeight="1" s="18">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>TURČIJA</t>
@@ -1315,7 +1326,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="23" ht="19.5" customHeight="1" s="17">
+    <row r="23" ht="19.5" customHeight="1" s="18">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>PARAGVAJ</t>
@@ -1333,7 +1344,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1348,7 +1359,7 @@
         <v>45469</v>
       </c>
     </row>
-    <row r="24" ht="19.5" customHeight="1" s="17">
+    <row r="24" ht="19.5" customHeight="1" s="18">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>TURČIJA</t>
@@ -1366,7 +1377,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1381,7 +1392,7 @@
         <v>45469</v>
       </c>
     </row>
-    <row r="25" ht="19.5" customHeight="1" s="17">
+    <row r="25" ht="19.5" customHeight="1" s="18">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>NEMČIJA</t>
@@ -1414,7 +1425,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="26" ht="19.5" customHeight="1" s="17">
+    <row r="26" ht="19.5" customHeight="1" s="18">
       <c r="A26" s="12" t="inlineStr">
         <is>
           <t>SLONOKOŠČENA O.</t>
@@ -1447,7 +1458,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="27" ht="19.5" customHeight="1" s="17">
+    <row r="27" ht="19.5" customHeight="1" s="18">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>NEMČIJA</t>
@@ -1480,7 +1491,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="28" ht="19.5" customHeight="1" s="17">
+    <row r="28" ht="19.5" customHeight="1" s="18">
       <c r="A28" s="3" t="inlineStr">
         <is>
           <t>EKVADOR</t>
@@ -1513,7 +1524,7 @@
         <v>45464</v>
       </c>
     </row>
-    <row r="29" ht="19.5" customHeight="1" s="17">
+    <row r="29" ht="19.5" customHeight="1" s="18">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>EKVADOR</t>
@@ -1531,7 +1542,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1546,7 +1557,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="30" ht="19.5" customHeight="1" s="17">
+    <row r="30" ht="19.5" customHeight="1" s="18">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>CURAÇAO</t>
@@ -1564,7 +1575,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1579,7 +1590,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="31" ht="19.5" customHeight="1" s="17">
+    <row r="31" ht="19.5" customHeight="1" s="18">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>NIZOZEMSKA</t>
@@ -1612,7 +1623,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="32" ht="19.5" customHeight="1" s="17">
+    <row r="32" ht="19.5" customHeight="1" s="18">
       <c r="A32" s="10" t="inlineStr">
         <is>
           <t>ŠVEDSKA</t>
@@ -1645,7 +1656,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="33" ht="19.5" customHeight="1" s="17">
+    <row r="33" ht="19.5" customHeight="1" s="18">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>NIZOZEMSKA</t>
@@ -1678,7 +1689,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="34" ht="19.5" customHeight="1" s="17">
+    <row r="34" ht="19.5" customHeight="1" s="18">
       <c r="A34" s="3" t="inlineStr">
         <is>
           <t>TUNIZIJA</t>
@@ -1711,7 +1722,7 @@
         <v>45464</v>
       </c>
     </row>
-    <row r="35" ht="19.5" customHeight="1" s="17">
+    <row r="35" ht="19.5" customHeight="1" s="18">
       <c r="A35" s="3" t="inlineStr">
         <is>
           <t>TUNIZIJA</t>
@@ -1729,7 +1740,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1744,7 +1755,7 @@
         <v>46199</v>
       </c>
     </row>
-    <row r="36" ht="19.5" customHeight="1" s="17">
+    <row r="36" ht="19.5" customHeight="1" s="18">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>JAPONSKA</t>
@@ -1762,7 +1773,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1777,7 +1788,7 @@
         <v>46199</v>
       </c>
     </row>
-    <row r="37" ht="19.5" customHeight="1" s="17">
+    <row r="37" ht="19.5" customHeight="1" s="18">
       <c r="A37" s="3" t="inlineStr">
         <is>
           <t>BELGIJA</t>
@@ -1810,7 +1821,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="38" ht="19.5" customHeight="1" s="17">
+    <row r="38" ht="19.5" customHeight="1" s="18">
       <c r="A38" s="3" t="inlineStr">
         <is>
           <t>IRAN</t>
@@ -1843,7 +1854,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="39" ht="19.5" customHeight="1" s="17">
+    <row r="39" ht="19.5" customHeight="1" s="18">
       <c r="A39" s="3" t="inlineStr">
         <is>
           <t>BELGIJA</t>
@@ -1876,7 +1887,7 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="40" ht="19.5" customHeight="1" s="17">
+    <row r="40" ht="19.5" customHeight="1" s="18">
       <c r="A40" s="9" t="inlineStr">
         <is>
           <t>N. ZELANDIJA</t>
@@ -1909,7 +1920,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="41" ht="19.5" customHeight="1" s="17">
+    <row r="41" ht="19.5" customHeight="1" s="18">
       <c r="A41" s="3" t="inlineStr">
         <is>
           <t>EGIPT</t>
@@ -1927,7 +1938,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1942,7 +1953,7 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="42" ht="19.5" customHeight="1" s="17">
+    <row r="42" ht="19.5" customHeight="1" s="18">
       <c r="A42" s="9" t="inlineStr">
         <is>
           <t>N. ZELANDIJA</t>
@@ -1960,7 +1971,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1975,7 +1986,7 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="43" ht="19.5" customHeight="1" s="17">
+    <row r="43" ht="19.5" customHeight="1" s="18">
       <c r="A43" s="3" t="inlineStr">
         <is>
           <t>ŠPANIJA</t>
@@ -2008,7 +2019,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="44" ht="19.5" customHeight="1" s="17">
+    <row r="44" ht="19.5" customHeight="1" s="18">
       <c r="A44" s="9" t="inlineStr">
         <is>
           <t>SAV. ARABIJA</t>
@@ -2041,7 +2052,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="45" ht="19.5" customHeight="1" s="17">
+    <row r="45" ht="19.5" customHeight="1" s="18">
       <c r="A45" s="3" t="inlineStr">
         <is>
           <t>ŠPANIJA</t>
@@ -2074,7 +2085,7 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="46" ht="19.5" customHeight="1" s="17">
+    <row r="46" ht="19.5" customHeight="1" s="18">
       <c r="A46" s="3" t="inlineStr">
         <is>
           <t>URUGVAJ</t>
@@ -2107,7 +2118,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="47" ht="19.5" customHeight="1" s="17">
+    <row r="47" ht="19.5" customHeight="1" s="18">
       <c r="A47" s="3" t="inlineStr">
         <is>
           <t>URUGVAJ</t>
@@ -2125,7 +2136,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2140,7 +2151,7 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="48" ht="19.5" customHeight="1" s="17">
+    <row r="48" ht="19.5" customHeight="1" s="18">
       <c r="A48" s="11" t="inlineStr">
         <is>
           <t>ZELENORTSKI O.</t>
@@ -2158,7 +2169,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2173,7 +2184,7 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="49" ht="19.5" customHeight="1" s="17">
+    <row r="49" ht="19.5" customHeight="1" s="18">
       <c r="A49" s="3" t="inlineStr">
         <is>
           <t>FRANCIJA</t>
@@ -2206,7 +2217,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="50" ht="19.5" customHeight="1" s="17">
+    <row r="50" ht="19.5" customHeight="1" s="18">
       <c r="A50" s="3" t="inlineStr">
         <is>
           <t>IRAK</t>
@@ -2239,7 +2250,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="51" ht="19.5" customHeight="1" s="17">
+    <row r="51" ht="19.5" customHeight="1" s="18">
       <c r="A51" s="3" t="inlineStr">
         <is>
           <t>FRANCIJA</t>
@@ -2272,7 +2283,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="52" ht="19.5" customHeight="1" s="17">
+    <row r="52" ht="19.5" customHeight="1" s="18">
       <c r="A52" s="3" t="inlineStr">
         <is>
           <t>NORVEŠKA</t>
@@ -2305,7 +2316,7 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="53" ht="19.5" customHeight="1" s="17">
+    <row r="53" ht="19.5" customHeight="1" s="18">
       <c r="A53" s="3" t="inlineStr">
         <is>
           <t>NORVEŠKA</t>
@@ -2323,7 +2334,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2338,7 +2349,7 @@
         <v>46199</v>
       </c>
     </row>
-    <row r="54" ht="19.5" customHeight="1" s="17">
+    <row r="54" ht="19.5" customHeight="1" s="18">
       <c r="A54" s="4" t="inlineStr">
         <is>
           <t>SENEGAL</t>
@@ -2356,7 +2367,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2371,7 +2382,7 @@
         <v>46199</v>
       </c>
     </row>
-    <row r="55" ht="19.5" customHeight="1" s="17">
+    <row r="55" ht="19.5" customHeight="1" s="18">
       <c r="A55" s="3" t="inlineStr">
         <is>
           <t>ARGENTINA</t>
@@ -2404,7 +2415,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="56" ht="19.5" customHeight="1" s="17">
+    <row r="56" ht="19.5" customHeight="1" s="18">
       <c r="A56" s="3" t="inlineStr">
         <is>
           <t>AVSTRIJA</t>
@@ -2437,7 +2448,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="57" ht="19.5" customHeight="1" s="17">
+    <row r="57" ht="19.5" customHeight="1" s="18">
       <c r="A57" s="3" t="inlineStr">
         <is>
           <t>ARGENTINA</t>
@@ -2470,7 +2481,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="58" ht="19.5" customHeight="1" s="17">
+    <row r="58" ht="19.5" customHeight="1" s="18">
       <c r="A58" s="3" t="inlineStr">
         <is>
           <t>JORDAN</t>
@@ -2503,7 +2514,7 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="59" ht="19.5" customHeight="1" s="17">
+    <row r="59" ht="19.5" customHeight="1" s="18">
       <c r="A59" s="3" t="inlineStr">
         <is>
           <t>JORDAN</t>
@@ -2521,7 +2532,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2536,7 +2547,7 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="60" ht="19.5" customHeight="1" s="17">
+    <row r="60" ht="19.5" customHeight="1" s="18">
       <c r="A60" s="13" t="inlineStr">
         <is>
           <t>ALŽIRIJA</t>
@@ -2554,7 +2565,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2569,7 +2580,7 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="61" ht="19.5" customHeight="1" s="17">
+    <row r="61" ht="19.5" customHeight="1" s="18">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>PORTUGALSKA</t>
@@ -2602,7 +2613,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="62" ht="19.5" customHeight="1" s="17">
+    <row r="62" ht="19.5" customHeight="1" s="18">
       <c r="A62" s="4" t="inlineStr">
         <is>
           <t>UZBEKISTAN</t>
@@ -2635,7 +2646,7 @@
         <v>46191</v>
       </c>
     </row>
-    <row r="63" ht="19.5" customHeight="1" s="17">
+    <row r="63" ht="19.5" customHeight="1" s="18">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>PORTUGALSKA</t>
@@ -2668,7 +2679,7 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="64" ht="19.5" customHeight="1" s="17">
+    <row r="64" ht="19.5" customHeight="1" s="18">
       <c r="A64" s="4" t="inlineStr">
         <is>
           <t>KOLUMBIJA</t>
@@ -2701,7 +2712,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="65" ht="19.5" customHeight="1" s="17">
+    <row r="65" ht="19.5" customHeight="1" s="18">
       <c r="A65" s="4" t="inlineStr">
         <is>
           <t>KOLUMBIJA</t>
@@ -2719,7 +2730,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2734,7 +2745,7 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="66" ht="19.5" customHeight="1" s="17">
+    <row r="66" ht="19.5" customHeight="1" s="18">
       <c r="A66" s="4" t="inlineStr">
         <is>
           <t>D.R. KONGO</t>
@@ -2752,7 +2763,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2767,7 +2778,7 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="67" ht="19.5" customHeight="1" s="17">
+    <row r="67" ht="19.5" customHeight="1" s="18">
       <c r="A67" s="3" t="inlineStr">
         <is>
           <t>ANGLIJA</t>
@@ -2800,7 +2811,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="68" ht="19.5" customHeight="1" s="17">
+    <row r="68" ht="19.5" customHeight="1" s="18">
       <c r="A68" s="10" t="inlineStr">
         <is>
           <t>GANA</t>
@@ -2833,7 +2844,7 @@
         <v>46191</v>
       </c>
     </row>
-    <row r="69" ht="19.5" customHeight="1" s="17">
+    <row r="69" ht="19.5" customHeight="1" s="18">
       <c r="A69" s="3" t="inlineStr">
         <is>
           <t>ANGLIJA</t>
@@ -2866,7 +2877,7 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="70" ht="19.5" customHeight="1" s="17">
+    <row r="70" ht="19.5" customHeight="1" s="18">
       <c r="A70" s="3" t="inlineStr">
         <is>
           <t>PANAMA</t>
@@ -2899,7 +2910,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="71" ht="19.5" customHeight="1" s="17">
+    <row r="71" ht="19.5" customHeight="1" s="18">
       <c r="A71" s="3" t="inlineStr">
         <is>
           <t>PANAMA</t>
@@ -2917,7 +2928,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2932,7 +2943,7 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="72" ht="19.5" customHeight="1" s="17">
+    <row r="72" ht="19.5" customHeight="1" s="18">
       <c r="A72" s="4" t="inlineStr">
         <is>
           <t>HRVAŠKA</t>
@@ -2950,7 +2961,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2965,23 +2976,23 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="73" ht="19.5" customHeight="1" s="17"/>
-    <row r="74" ht="23.25" customHeight="1" s="17">
+    <row r="73" ht="19.5" customHeight="1" s="18"/>
+    <row r="74" ht="23.25" customHeight="1" s="18">
       <c r="A74" s="14" t="n"/>
     </row>
-    <row r="75" ht="21" customHeight="1" s="17">
+    <row r="75" ht="21" customHeight="1" s="18">
       <c r="A75" s="8" t="n"/>
       <c r="B75" s="7" t="n"/>
       <c r="C75" s="6" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="n"/>
+      <c r="A77" s="17" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="n"/>
+      <c r="A78" s="17" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="n"/>
+      <c r="A79" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3004,7 +3015,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3102,7 +3113,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3125,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3127,7 +3138,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3163,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3188,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3213,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3238,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3263,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3288,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3313,1526 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22.42578125" bestFit="1" customWidth="1" style="18" min="2" max="2"/>
+    <col width="18.85546875" bestFit="1" customWidth="1" style="18" min="3" max="3"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="18" min="5" max="5"/>
+    <col width="12.42578125" bestFit="1" customWidth="1" style="18" min="6" max="7"/>
+    <col width="23" bestFit="1" customWidth="1" style="18" min="8" max="8"/>
+    <col width="23.42578125" bestFit="1" customWidth="1" style="18" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ekipa1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Ekipa2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Obdelana tekma</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Polje ekipe 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Polje ekipe 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Polje napredujoče ekipe</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Št. Točk</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Stolpec rezultata - tekma</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>NEMČIJA</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>PARAGVAJ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>29.6.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>E11</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FRANCIJA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ŠVEDSKA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>30.6.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>J. AFRIKA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>KANADA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>28.6.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>B22</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B26</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>E24</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NIZOZEMSKA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MAROKO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>30.6.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>B28</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>B32</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>E30</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PORTUGALSKA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HRVAŠKA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.7.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>B34</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>B38</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>E36</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ŠPANIJA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AVSTRIJA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.7.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>B40</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>B44</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>E42</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ZDA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BIH</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.7.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>B47</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>B51</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>E49</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BELGIJA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SENEGAL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.7.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>B53</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>B57</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>E55</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BRAZILIJA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>JAPONSKA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>29.6.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>B59</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>B63</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>E61</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SLONOKOŠČENA OBALA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NORVEŠKA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>30.6.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>B65</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>B69</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>E67</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MEHIKA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EKVADOR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.7.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>B72</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>B76</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>E74</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ANGLIJA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DR KONGO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.7.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>B78</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>B82</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>E80</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ARGENTINA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ZELENORTSKI OTOKI</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.7.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>B84</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>B88</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>E86</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AVSTRALIJA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EGIPT</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3.7.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>B90</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>B94</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>E92</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ŠVICA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ALŽIRIJA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.7.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>B97</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>B101</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>E99</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KOLUMBIJA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GANA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>B103</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>B107</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>E105</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4.7.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>E11</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>H14</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KANADA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4.7.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>E24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>E30</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>H27</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6.7.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>E36</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>E42</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>H39</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>AO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>7.7.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>E49</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>E55</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>H52</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>AQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5.7.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>E61</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>E67</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>H64</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6.7.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>E74</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>E80</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>H77</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7.7.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>E86</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>E92</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>H89</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>7.7.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>E99</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>E105</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>H102</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>AY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>9.7.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>H14</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>H27</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>K19</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>10.7.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>H39</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>H52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>K44</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>11.7.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>H64</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>H77</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>K69</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>12.7.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>H89</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>H102</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>K94</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>14.7.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>K19</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>K44</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O32</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>15.7.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>K69</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>K94</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>O82</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>T15</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>U21</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>BM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>O32</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>O82</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>T56</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>BO</t>
         </is>
       </c>
     </row>

--- a/SP 2026 - tekme.xlsx
+++ b/SP 2026 - tekme.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-23148" yWindow="-852" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tekme" sheetId="1" state="visible" r:id="rId1"/>
@@ -592,11 +592,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M79"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="15.7109375" customWidth="1" style="18" min="1" max="1"/>
-    <col width="2.140625" customWidth="1" style="18" min="2" max="2"/>
-    <col width="15.7109375" customWidth="1" style="18" min="3" max="3"/>
+    <col width="15.6640625" customWidth="1" style="18" min="1" max="1"/>
+    <col width="2.109375" customWidth="1" style="18" min="2" max="2"/>
+    <col width="15.6640625" customWidth="1" style="18" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1" s="18">
@@ -3015,7 +3015,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3329,14 +3329,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="22.42578125" bestFit="1" customWidth="1" style="18" min="2" max="2"/>
-    <col width="18.85546875" bestFit="1" customWidth="1" style="18" min="3" max="3"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="18" min="5" max="5"/>
-    <col width="12.42578125" bestFit="1" customWidth="1" style="18" min="6" max="7"/>
+    <col width="22.44140625" bestFit="1" customWidth="1" style="18" min="2" max="2"/>
+    <col width="18.88671875" bestFit="1" customWidth="1" style="18" min="3" max="3"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="18" min="5" max="5"/>
+    <col width="12.44140625" bestFit="1" customWidth="1" style="18" min="6" max="7"/>
     <col width="23" bestFit="1" customWidth="1" style="18" min="8" max="8"/>
-    <col width="23.42578125" bestFit="1" customWidth="1" style="18" min="10" max="10"/>
+    <col width="23.44140625" bestFit="1" customWidth="1" style="18" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>AJ</t>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -4197,6 +4197,16 @@
           <t>R8</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PARAGVAJ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>FRANCIJA</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>4.7.</t>
@@ -4204,7 +4214,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4242,6 +4252,11 @@
           <t>KANADA</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MAROKO</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>4.7.</t>
@@ -4249,7 +4264,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4282,6 +4297,16 @@
           <t>R8</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PORTUGALSKA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ŠPANIJA</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>6.7.</t>
@@ -4289,7 +4314,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4322,6 +4347,16 @@
           <t>R8</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ZDA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BELGIJA</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>7.7.</t>
@@ -4329,7 +4364,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4362,6 +4397,16 @@
           <t>R8</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BRAZILIJA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NORVEŠKA</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>5.7.</t>
@@ -4369,7 +4414,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4402,6 +4447,16 @@
           <t>R8</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MEHIKA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ANGLIJA</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>6.7.</t>
@@ -4409,7 +4464,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4442,6 +4497,16 @@
           <t>R8</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ARGENTINA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EGIPT</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>7.7.</t>
@@ -4482,6 +4547,16 @@
           <t>R8</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ŠVICA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>KOLUMBIJA</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>7.7.</t>
@@ -4522,6 +4597,16 @@
           <t>R4</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FRANCIJA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MAROKO</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>9.7.</t>
@@ -4562,6 +4647,16 @@
           <t>R4</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ŠPANIJA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BELGIJA</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>10.7.</t>
@@ -4600,6 +4695,16 @@
       <c r="A28" t="inlineStr">
         <is>
           <t>R4</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NORVEŠKA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ANGLIJA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
